--- a/data/trans_dic/P68-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P68-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 25,41</t>
+          <t>17,05; 25,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,33; 34,33</t>
+          <t>23,88; 34,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,31; 28,97</t>
+          <t>17,43; 28,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,02; 26,82</t>
+          <t>16,67; 26,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,26; 27,85</t>
+          <t>14,88; 27,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,67; 29,18</t>
+          <t>16,15; 30,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,99</t>
+          <t>13,11; 23,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 25,59</t>
+          <t>17,14; 25,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,39; 24,65</t>
+          <t>17,71; 25,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,04; 30,82</t>
+          <t>22,03; 30,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 24,79</t>
+          <t>16,94; 24,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,98; 24,82</t>
+          <t>18,24; 24,98</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,99; 30,51</t>
+          <t>22,65; 30,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,11; 27,94</t>
+          <t>18,85; 27,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 28,4</t>
+          <t>19,3; 27,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 21,31</t>
+          <t>6,26; 21,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 25,99</t>
+          <t>15,4; 25,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,88; 29,81</t>
+          <t>18,41; 28,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,5; 25,3</t>
+          <t>16,03; 25,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,15; 28,94</t>
+          <t>21,75; 28,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 27,43</t>
+          <t>21,04; 27,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,25; 26,56</t>
+          <t>19,99; 26,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,37; 25,79</t>
+          <t>19,23; 25,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 23,02</t>
+          <t>9,01; 23,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,45; 32,09</t>
+          <t>22,54; 32,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,85; 30,28</t>
+          <t>20,44; 30,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,48; 35,4</t>
+          <t>25,66; 35,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 21,19</t>
+          <t>12,66; 21,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 27,84</t>
+          <t>16,41; 27,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,22; 31,72</t>
+          <t>18,81; 31,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,28; 29,4</t>
+          <t>19,77; 30,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,95; 52,38</t>
+          <t>21,2; 52,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,98; 29,12</t>
+          <t>21,81; 28,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,6; 28,65</t>
+          <t>20,83; 28,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,13; 31,75</t>
+          <t>24,23; 30,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 36,02</t>
+          <t>17,88; 36,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,21; 28,47</t>
+          <t>21,28; 28,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,44; 23,88</t>
+          <t>15,39; 22,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 26,54</t>
+          <t>18,17; 26,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,65; 26,07</t>
+          <t>17,91; 26,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 27,23</t>
+          <t>18,52; 27,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 26,14</t>
+          <t>16,6; 26,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,19; 25,66</t>
+          <t>15,89; 25,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 26,93</t>
+          <t>13,22; 26,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,01; 26,52</t>
+          <t>21,04; 26,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 23,16</t>
+          <t>17,0; 23,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 24,7</t>
+          <t>18,65; 24,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 25,23</t>
+          <t>16,87; 24,71</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,82; 26,77</t>
+          <t>22,95; 26,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,2; 25,66</t>
+          <t>21,21; 25,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,58; 27,28</t>
+          <t>22,46; 27,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,41; 20,79</t>
+          <t>11,41; 20,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,41</t>
+          <t>19,23; 24,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,07; 25,82</t>
+          <t>20,11; 25,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,57; 23,82</t>
+          <t>18,4; 23,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,89; 30,1</t>
+          <t>20,51; 29,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,11; 25,31</t>
+          <t>22,16; 25,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 24,82</t>
+          <t>21,41; 24,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,5; 25,1</t>
+          <t>21,42; 24,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,17</t>
+          <t>16,16; 23,37</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>62882; 96354</t>
+          <t>64651; 94876</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62742; 92313</t>
+          <t>64228; 93602</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44148; 69834</t>
+          <t>42027; 69751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56546; 89090</t>
+          <t>55390; 87901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23601; 43072</t>
+          <t>23011; 42974</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25266; 47055</t>
+          <t>26040; 49076</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20493; 39906</t>
+          <t>21813; 39719</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44184; 65995</t>
+          <t>44208; 66229</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92816; 131604</t>
+          <t>94512; 134657</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94817; 132593</t>
+          <t>94778; 131923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68948; 101015</t>
+          <t>69005; 101075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>106092; 146449</t>
+          <t>107666; 147426</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126865; 168382</t>
+          <t>125011; 169085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78103; 114205</t>
+          <t>77025; 111032</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80470; 115963</t>
+          <t>78810; 113061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42949; 170744</t>
+          <t>50177; 173635</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41270; 69152</t>
+          <t>40992; 67529</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51274; 80962</t>
+          <t>50013; 78594</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42441; 69255</t>
+          <t>43893; 69112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83476; 114214</t>
+          <t>85815; 114083</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>173133; 224370</t>
+          <t>172114; 223680</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137764; 180692</t>
+          <t>135994; 179462</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>132093; 175926</t>
+          <t>131189; 174781</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93178; 275265</t>
+          <t>107780; 276286</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91471; 130743</t>
+          <t>91825; 130773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64003; 97622</t>
+          <t>65886; 97227</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92165; 128031</t>
+          <t>92818; 129291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41510; 71472</t>
+          <t>42689; 72105</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34434; 59327</t>
+          <t>34976; 57945</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41196; 67986</t>
+          <t>40318; 66996</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51980; 79272</t>
+          <t>53292; 81305</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66064; 165148</t>
+          <t>66835; 165115</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>136368; 180696</t>
+          <t>135314; 179633</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110565; 153766</t>
+          <t>111793; 154599</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152324; 200433</t>
+          <t>152958; 195174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>117009; 235031</t>
+          <t>116681; 237233</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>117713; 158000</t>
+          <t>118109; 160618</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64646; 99991</t>
+          <t>64434; 95748</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72569; 105946</t>
+          <t>72559; 105597</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82978; 122579</t>
+          <t>84236; 122528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73476; 105527</t>
+          <t>71770; 106432</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50001; 78802</t>
+          <t>50053; 78559</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52174; 82719</t>
+          <t>51225; 82942</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64619; 128579</t>
+          <t>63140; 127603</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>198045; 249947</t>
+          <t>198277; 252820</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>123368; 166773</t>
+          <t>122456; 167168</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134307; 178264</t>
+          <t>134553; 179049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>160297; 239122</t>
+          <t>159833; 234171</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>432161; 506905</t>
+          <t>434510; 510003</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>300778; 363978</t>
+          <t>300958; 365159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>318451; 384700</t>
+          <t>316701; 384864</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>221407; 403545</t>
+          <t>221500; 403377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>195809; 249326</t>
+          <t>196389; 247541</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>190384; 244971</t>
+          <t>190759; 242807</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>191645; 245787</t>
+          <t>189877; 242026</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>301871; 435034</t>
+          <t>296499; 430214</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>644460; 737682</t>
+          <t>646055; 740870</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>506992; 587553</t>
+          <t>506861; 591211</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>525085; 613144</t>
+          <t>523190; 606579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>547345; 784691</t>
+          <t>547157; 791217</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P68-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P68-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 25,02</t>
+          <t>17,1; 25,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,88; 34,8</t>
+          <t>23,63; 34,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,43; 28,93</t>
+          <t>17,47; 28,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,67; 26,46</t>
+          <t>16,25; 25,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 27,79</t>
+          <t>14,84; 27,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 30,43</t>
+          <t>15,88; 29,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 23,88</t>
+          <t>12,77; 23,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 25,68</t>
+          <t>17,82; 26,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 25,23</t>
+          <t>17,49; 25,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 30,66</t>
+          <t>22,02; 30,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 24,81</t>
+          <t>16,61; 24,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 24,98</t>
+          <t>17,98; 24,51</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,65; 30,64</t>
+          <t>22,75; 30,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 27,17</t>
+          <t>18,88; 27,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,3; 27,69</t>
+          <t>19,78; 28,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 21,67</t>
+          <t>17,8; 25,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 25,38</t>
+          <t>15,17; 24,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 28,94</t>
+          <t>18,43; 29,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,03; 25,24</t>
+          <t>15,51; 25,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,75; 28,91</t>
+          <t>21,25; 28,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,04; 27,34</t>
+          <t>21,22; 27,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,99; 26,38</t>
+          <t>19,84; 26,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 25,62</t>
+          <t>19,19; 25,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 23,1</t>
+          <t>19,83; 25,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,54; 32,1</t>
+          <t>22,1; 31,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,44; 30,16</t>
+          <t>20,1; 30,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,66; 35,75</t>
+          <t>25,21; 35,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,38</t>
+          <t>12,86; 21,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 27,19</t>
+          <t>16,45; 27,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 31,26</t>
+          <t>19,15; 31,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 30,16</t>
+          <t>18,92; 29,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,2; 52,36</t>
+          <t>17,62; 25,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,81; 28,95</t>
+          <t>21,62; 29,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,83; 28,8</t>
+          <t>20,97; 29,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,23; 30,92</t>
+          <t>24,53; 31,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 36,35</t>
+          <t>16,14; 22,43</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,28; 28,94</t>
+          <t>21,04; 28,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,39; 22,87</t>
+          <t>16,05; 23,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,17; 26,45</t>
+          <t>18,14; 26,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 26,06</t>
+          <t>17,3; 25,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 27,46</t>
+          <t>18,72; 26,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 26,06</t>
+          <t>16,87; 26,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,89; 25,73</t>
+          <t>16,09; 25,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,22; 26,72</t>
+          <t>20,72; 27,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,04; 26,82</t>
+          <t>21,09; 26,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,0; 23,21</t>
+          <t>17,2; 23,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,65; 24,81</t>
+          <t>18,43; 24,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 24,71</t>
+          <t>20,03; 25,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,95; 26,94</t>
+          <t>22,72; 26,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,21; 25,74</t>
+          <t>21,07; 25,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,29</t>
+          <t>22,39; 27,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,41; 20,78</t>
+          <t>18,15; 22,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,23; 24,23</t>
+          <t>18,7; 24,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,11; 25,59</t>
+          <t>20,1; 25,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,4; 23,45</t>
+          <t>18,53; 23,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,51; 29,77</t>
+          <t>21,32; 25,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,16; 25,42</t>
+          <t>22,24; 25,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,41; 24,97</t>
+          <t>21,35; 24,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 24,84</t>
+          <t>21,43; 24,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,37</t>
+          <t>20,0; 22,99</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71215</t>
+          <t>75044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54681</t>
+          <t>59821</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>125897</t>
+          <t>134865</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64651; 94876</t>
+          <t>64843; 98145</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64228; 93602</t>
+          <t>63556; 93736</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42027; 69751</t>
+          <t>42124; 69589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55390; 87901</t>
+          <t>59472; 92762</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23011; 42974</t>
+          <t>22955; 42740</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26040; 49076</t>
+          <t>25613; 47072</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21813; 39719</t>
+          <t>21245; 39799</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44208; 66229</t>
+          <t>49776; 73622</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94512; 134657</t>
+          <t>93359; 133607</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94778; 131923</t>
+          <t>94753; 131267</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69005; 101075</t>
+          <t>67656; 100221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>107666; 147426</t>
+          <t>116000; 158184</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111983</t>
+          <t>132997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98730</t>
+          <t>107455</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>210712</t>
+          <t>240452</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125011; 169085</t>
+          <t>125571; 169561</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77025; 111032</t>
+          <t>77166; 111898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78810; 113061</t>
+          <t>80785; 117457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50177; 173635</t>
+          <t>111006; 158980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40992; 67529</t>
+          <t>40374; 66087</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50013; 78594</t>
+          <t>50056; 80505</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43893; 69112</t>
+          <t>42467; 70931</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85815; 114083</t>
+          <t>93612; 124352</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>172114; 223680</t>
+          <t>173584; 225160</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135994; 179462</t>
+          <t>134943; 181687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131189; 174781</t>
+          <t>130929; 176681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>107780; 276286</t>
+          <t>211110; 269155</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55277</t>
+          <t>68862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96908</t>
+          <t>70712</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>152184</t>
+          <t>139574</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91825; 130773</t>
+          <t>90022; 129831</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65886; 97227</t>
+          <t>64799; 96910</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92818; 129291</t>
+          <t>91172; 127444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42689; 72105</t>
+          <t>51584; 86538</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34976; 57945</t>
+          <t>35059; 59307</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40318; 66996</t>
+          <t>41043; 67291</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53292; 81305</t>
+          <t>51011; 79081</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66835; 165115</t>
+          <t>58007; 84712</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135314; 179633</t>
+          <t>134151; 181405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111793; 154599</t>
+          <t>112534; 156744</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152958; 195174</t>
+          <t>154833; 196432</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>116681; 237233</t>
+          <t>117837; 163762</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101030</t>
+          <t>108107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>103896</t>
+          <t>107345</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>204926</t>
+          <t>215452</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>118109; 160618</t>
+          <t>116747; 159018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64434; 95748</t>
+          <t>67209; 97887</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72559; 105597</t>
+          <t>72435; 105055</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84236; 122528</t>
+          <t>89243; 129283</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71770; 106432</t>
+          <t>72577; 103736</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50053; 78559</t>
+          <t>50866; 79355</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51225; 82942</t>
+          <t>51869; 82325</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63140; 127603</t>
+          <t>92252; 123135</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>198277; 252820</t>
+          <t>198810; 250606</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122456; 167168</t>
+          <t>123889; 169410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134553; 179049</t>
+          <t>133009; 177951</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>159833; 234171</t>
+          <t>192546; 242445</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>354215</t>
+          <t>345334</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>693720</t>
+          <t>730344</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>434510; 510003</t>
+          <t>430098; 508849</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>300958; 365159</t>
+          <t>298880; 363016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316701; 384864</t>
+          <t>315797; 384409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>221500; 403377</t>
+          <t>345993; 427477</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>196389; 247541</t>
+          <t>190991; 247029</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>190759; 242807</t>
+          <t>190709; 245637</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>189877; 242026</t>
+          <t>191223; 242145</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>296499; 430214</t>
+          <t>318644; 374504</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>646055; 740870</t>
+          <t>648329; 738299</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>506861; 591211</t>
+          <t>505548; 585496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>523190; 606579</t>
+          <t>523285; 608126</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>547157; 791217</t>
+          <t>680340; 782010</t>
         </is>
       </c>
     </row>
